--- a/data/analysis_results/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>model1-first</t>
-  </si>
-  <si>
-    <t>model2-first</t>
+    <t>Qwen/Qwen2-0.5B-Instruct-first</t>
+  </si>
+  <si>
+    <t>gpt-4.1-first</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>10</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/data/analysis_results/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>Qwen/Qwen2-0.5B-Instruct-first</t>
-  </si>
-  <si>
-    <t>gpt-4.1-first</t>
+    <t>model1-first</t>
+  </si>
+  <si>
+    <t>model2-first</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>10</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>8</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>426</v>
